--- a/sampleprojects/CorporateTax/excel/states/MO_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/MO_corp.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>DT: Determine MO Filing Requirement</t>
   </si>
@@ -70,7 +70,7 @@
     <t>Meets economic nexus threshold ($100K gross receipts); result.mo_gross_receipts is greater than or equal to result.mo_economic_nexus_threshold</t>
   </si>
   <si>
-    <t>result.mo_gross_receipts &gt;= result.mo_economic_nexus_threshold</t>
+    <t>mo_result.gross_receipts &gt;= mo_result.economic_nexus_threshold</t>
   </si>
   <si>
     <t>-</t>
@@ -85,7 +85,7 @@
     <t>Physical nexus - filing required</t>
   </si>
   <si>
-    <t>set result.mo_has_nexus = true;</t>
+    <t>set mo_result.has_nexus = true;</t>
   </si>
   <si>
     <t>X</t>
@@ -97,7 +97,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set result.mo_has_nexus = false; set result.mo_tax_liability = 0.0;</t>
+    <t>set mo_result.has_nexus = false; set mo_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate MO Income Adjustments</t>
@@ -115,19 +115,19 @@
     <t>Has Missouri nexus</t>
   </si>
   <si>
-    <t>result.mo_has_nexus is equal to true</t>
+    <t>mo_result.has_nexus is equal to true</t>
   </si>
   <si>
     <t>Calculate Missouri state additions and subtractions (including 50% federal tax deduction); Calculate state-specific income adjustments</t>
   </si>
   <si>
-    <t>set result.mo_state_additions = 0.0; if result.mo_us_interest_income != 0.0 then set result.mo_state_additions = result.mo_state_additions + result.mo_us_interest_income; endif set result.mo_state_subtractions = 0.0; set result.mo_state_subtractions = result.mo_state_subtractions + result.federal_tax_liability * result.mo_federal_tax_deduction_percentage; if result.mo_municipal_interest != 0.0 then set result.mo_state_subtractions = result.mo_state_subtractions + result.mo_municipal_interest; endif add (("Missouri additions: $" + string value of (result.mo_state_additions)) + ", subtractions: $") + string value of (result.mo_state_subtractions) to job.audit_trail; add "Missouri 50% federal tax deduction: $" + string value of (result.federal_tax_liability * result.mo_federal_tax_deduction_percentage) to job.audit_trail;</t>
+    <t>set mo_result.state_additions = 0.0; if mo_result.us_interest_income != 0.0 then set mo_result.state_additions = mo_result.state_additions + mo_result.us_interest_income; endif set mo_result.state_subtractions = 0.0; set mo_result.state_subtractions = mo_result.state_subtractions + result.federal_tax_liability * result.mo_federal_tax_deduction_percentage; if mo_result.municipal_interest != 0.0 then set mo_result.state_subtractions = mo_result.state_subtractions + mo_result.municipal_interest; endif add (("Missouri additions: $" + string value of (mo_result.state_additions)) + ", subtractions: $") + string value of (mo_result.state_subtractions) to job.audit_trail; add "Missouri 50% federal tax deduction: $" + string value of (result.federal_tax_liability * result.mo_federal_tax_deduction_percentage) to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no adjustments</t>
   </si>
   <si>
-    <t>set result.mo_state_additions = 0.0; set result.mo_state_subtractions = 0.0;</t>
+    <t>set mo_result.state_additions = 0.0; set mo_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate MO State Tax</t>
@@ -145,19 +145,19 @@
     <t>Has positive taxable income; result.mo_apportioned_income is greater than 0</t>
   </si>
   <si>
-    <t>result.mo_apportioned_income &gt; 0.0</t>
+    <t>mo_result.apportioned_income &gt; 0.0</t>
   </si>
   <si>
     <t>Calculate Missouri corporate tax (flat rate 4.0%); Apply Missouri 4.0% flat rate</t>
   </si>
   <si>
-    <t>set result.mo_taxable_income = the maximum of (result.mo_apportioned_income + result.mo_state_additions - result.mo_state_subtractions) and (0.0); set result.mo_tax_liability = the maximum of (result.mo_taxable_income * result.mo_corp_tax_rate - result.mo_state_credits) and (0.0); set result.mo_refund_or_owed = result.mo_estimated_payments - result.mo_tax_liability; add "Missouri taxable income: $" + string value of (result.mo_taxable_income) to job.audit_trail; add "Missouri tax liability (4.0%, effective ~3.6% after 50% federal tax deduction): $" + string value of (result.mo_tax_liability) to job.audit_trail;</t>
+    <t>set mo_result.taxable_income = the maximum of (mo_result.apportioned_income + mo_result.state_additions - mo_result.state_subtractions) and (0.0); set mo_result.tax_liability = the maximum of (mo_result.taxable_income * mo_result.corp_tax_rate - mo_result.state_credits) and (0.0); set mo_result.refund_or_owed = mo_result.estimated_payments - mo_result.tax_liability; add "Missouri taxable income: $" + string value of (mo_result.taxable_income) to job.audit_trail; add "Missouri tax liability (4.0%, effective ~3.6% after 50% federal tax deduction): $" + string value of (mo_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>No taxable income - no tax liability</t>
   </si>
   <si>
-    <t>set result.mo_taxable_income = 0.0; set result.mo_tax_liability = 0.0;</t>
+    <t>set mo_result.taxable_income = 0.0; set mo_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
@@ -205,10 +205,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(9 attributes)</t>
+    <t>mo_apportionment</t>
+  </si>
+  <si>
+    <t>(5 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -238,7 +238,7 @@
     <t>Missouri economic nexus gross receipts threshold: $100,000</t>
   </si>
   <si>
-    <t>mo_federal_tax_deduction_percentage</t>
+    <t>federal_tax_deduction_percentage</t>
   </si>
   <si>
     <t>0.50</t>
@@ -247,118 +247,88 @@
     <t>Missouri allows deduction of 50% of federal income tax paid - MO Rev. Stat. § 143.121</t>
   </si>
   <si>
+    <t>state_tax_rate</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>Missouri corporate income tax rate: 4.0% flat rate - MO Rev. Stat. § 143.071</t>
+  </si>
+  <si>
+    <t>transaction_threshold</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Missouri does not have a transaction count threshold</t>
+  </si>
+  <si>
+    <t>mo_result</t>
+  </si>
+  <si>
+    <t>(14 attributes)</t>
+  </si>
+  <si>
+    <t>apportioned_income</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>Declared from decision-table usage; referenced by MO but never declared (campaign #948 Phase 1)</t>
+  </si>
+  <si>
+    <t>corp_tax_rate</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>MO-1120 instructions LINE 14: line 13 multiplied by 4 percent</t>
+  </si>
+  <si>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
+  </si>
+  <si>
+    <t>has_nexus</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>municipal_interest</t>
+  </si>
+  <si>
+    <t>refund_or_owed</t>
+  </si>
+  <si>
     <t>state_additions</t>
   </si>
   <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>Missouri additions: federal interest income, certain expenses, IRC 199A addback, etc.</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>Missouri state code</t>
-  </si>
-  <si>
     <t>state_credits</t>
   </si>
   <si>
-    <t>Missouri tax credits: jobs creation, historic preservation, film production, etc.</t>
-  </si>
-  <si>
     <t>state_subtractions</t>
   </si>
   <si>
-    <t>Missouri subtractions: 50% federal tax deduction, MO municipal interest, state NOL, etc.</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
-    <t>0.040</t>
-  </si>
-  <si>
-    <t>Missouri corporate income tax rate: 4.0% flat rate - MO Rev. Stat. § 143.071</t>
-  </si>
-  <si>
-    <t>transaction_threshold</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Missouri does not have a transaction count threshold</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>(14 attributes)</t>
-  </si>
-  <si>
-    <t>mo_apportioned_income</t>
-  </si>
-  <si>
-    <t>Declared from decision-table usage; referenced by MO but never declared (campaign #948 Phase 1)</t>
-  </si>
-  <si>
-    <t>mo_corp_tax_rate</t>
-  </si>
-  <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>MO-1120 instructions LINE 14: line 13 multiplied by 4 percent</t>
-  </si>
-  <si>
-    <t>mo_economic_nexus_threshold</t>
-  </si>
-  <si>
-    <t>mo_estimated_payments</t>
-  </si>
-  <si>
-    <t>mo_gross_receipts</t>
-  </si>
-  <si>
-    <t>mo_has_nexus</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>mo_municipal_interest</t>
-  </si>
-  <si>
-    <t>mo_refund_or_owed</t>
-  </si>
-  <si>
-    <t>mo_state_additions</t>
-  </si>
-  <si>
-    <t>mo_state_credits</t>
-  </si>
-  <si>
-    <t>mo_state_subtractions</t>
-  </si>
-  <si>
-    <t>mo_tax_liability</t>
-  </si>
-  <si>
-    <t>mo_taxable_income</t>
-  </si>
-  <si>
-    <t>mo_us_interest_income</t>
+    <t>tax_liability</t>
+  </si>
+  <si>
+    <t>taxable_income</t>
+  </si>
+  <si>
+    <t>us_interest_income</t>
   </si>
 </sst>
 </file>
@@ -2751,14 +2721,14 @@
       <c r="B8" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>65</v>
+      <c r="C8" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
@@ -2767,7 +2737,7 @@
         <v>67</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -2786,52 +2756,30 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="16" t="s">
+      <c r="A9" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="B9" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>70</v>
@@ -2840,7 +2788,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>8</v>
@@ -2849,7 +2797,7 @@
         <v>67</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -2872,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>70</v>
@@ -2881,7 +2829,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
@@ -2890,7 +2838,7 @@
         <v>67</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -2913,16 +2861,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
@@ -2931,7 +2879,7 @@
         <v>67</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -2950,30 +2898,52 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
+      <c r="A13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>70</v>
@@ -2982,7 +2952,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
@@ -2991,7 +2961,7 @@
         <v>67</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -3014,16 +2984,16 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>70</v>
+        <v>93</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>94</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
@@ -3032,7 +3002,7 @@
         <v>67</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -3055,7 +3025,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>70</v>
@@ -3064,7 +3034,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
@@ -3073,7 +3043,7 @@
         <v>67</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -3096,7 +3066,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>70</v>
@@ -3105,7 +3075,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>8</v>
@@ -3114,7 +3084,7 @@
         <v>67</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -3137,7 +3107,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>70</v>
@@ -3146,7 +3116,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
@@ -3155,7 +3125,7 @@
         <v>67</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -3178,16 +3148,16 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
@@ -3196,7 +3166,7 @@
         <v>67</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -3219,7 +3189,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>70</v>
@@ -3228,7 +3198,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>8</v>
@@ -3237,7 +3207,7 @@
         <v>67</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>8</v>
@@ -3260,7 +3230,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>70</v>
@@ -3269,7 +3239,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>8</v>
@@ -3278,7 +3248,7 @@
         <v>67</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>8</v>
@@ -3301,7 +3271,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>70</v>
@@ -3310,7 +3280,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>8</v>
@@ -3319,7 +3289,7 @@
         <v>67</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>8</v>
@@ -3342,7 +3312,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>70</v>
@@ -3351,7 +3321,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>8</v>
@@ -3360,7 +3330,7 @@
         <v>67</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>8</v>
@@ -3375,170 +3345,6 @@
         <v>8</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M27" s="8" t="s">
         <v>8</v>
       </c>
     </row>
